--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="1" r:id="Rd5a0a3986c7344c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="1" r:id="R0cbd4bd8a5cb47c5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -177,7 +177,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="44">
+  <x:cellXfs count="46">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -195,102 +195,96 @@
       </x:extLst>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
@@ -298,56 +292,73 @@
       </x:extLst>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
@@ -587,399 +598,399 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="31" t="str">
+      <x:c r="A1" s="33" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B1" s="12" t="str">
+      <x:c r="B1" s="14" t="str">
         <x:v>full_name</x:v>
       </x:c>
-      <x:c r="C1" s="12" t="str">
+      <x:c r="C1" s="14" t="str">
         <x:v>value_type</x:v>
       </x:c>
-      <x:c r="D1" s="12" t="str">
+      <x:c r="D1" s="14" t="str">
         <x:v>read_schema_from_file</x:v>
       </x:c>
-      <x:c r="E1" s="12" t="str">
+      <x:c r="E1" s="14" t="str">
         <x:v>input</x:v>
       </x:c>
-      <x:c r="F1" s="12" t="str">
+      <x:c r="F1" s="14" t="str">
         <x:v>index</x:v>
       </x:c>
-      <x:c r="G1" s="12" t="str">
+      <x:c r="G1" s="14" t="str">
         <x:v>mode</x:v>
       </x:c>
-      <x:c r="H1" s="12" t="str">
+      <x:c r="H1" s="14" t="str">
         <x:v>group</x:v>
       </x:c>
-      <x:c r="I1" s="12" t="str">
+      <x:c r="I1" s="14" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="J1" s="12" t="str">
+      <x:c r="J1" s="14" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="K1" s="13" t="str">
+      <x:c r="K1" s="15" t="str">
         <x:v>output</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="35" t="str">
+      <x:c r="A2" s="37" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B2" s="16" t="str">
+      <x:c r="B2" s="18" t="str">
         <x:v>完整表名</x:v>
       </x:c>
-      <x:c r="C2" s="16" t="str">
+      <x:c r="C2" s="18" t="str">
         <x:v>记录类型</x:v>
       </x:c>
-      <x:c r="D2" s="16" t="str">
+      <x:c r="D2" s="18" t="str">
         <x:v>从业务表读取定义</x:v>
       </x:c>
-      <x:c r="E2" s="16" t="str">
+      <x:c r="E2" s="18" t="str">
         <x:v>输入文件</x:v>
       </x:c>
-      <x:c r="F2" s="16" t="str">
+      <x:c r="F2" s="18" t="str">
         <x:v>索引字段</x:v>
       </x:c>
-      <x:c r="G2" s="16" t="str">
+      <x:c r="G2" s="18" t="str">
         <x:v>模式</x:v>
       </x:c>
-      <x:c r="H2" s="16" t="str">
+      <x:c r="H2" s="18" t="str">
         <x:v>分组</x:v>
       </x:c>
-      <x:c r="I2" s="16" t="str">
+      <x:c r="I2" s="18" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="J2" s="16"/>
-      <x:c r="K2" s="16" t="str">
+      <x:c r="J2" s="18"/>
+      <x:c r="K2" s="18" t="str">
         <x:v>输出文件</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="36" t="str">
+      <x:c r="A3" s="38" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3" s="18"/>
-      <x:c r="C3" s="18"/>
-      <x:c r="D3" s="18" t="str">
+      <x:c r="B3" s="20"/>
+      <x:c r="C3" s="20"/>
+      <x:c r="D3" s="20" t="str">
         <x:v>必须为 true</x:v>
       </x:c>
-      <x:c r="E3" s="18"/>
-      <x:c r="F3" s="18" t="str">
+      <x:c r="E3" s="20"/>
+      <x:c r="F3" s="20" t="str">
         <x:v>统一使用 id</x:v>
       </x:c>
-      <x:c r="G3" s="18" t="str">
+      <x:c r="G3" s="20" t="str">
         <x:v>统一使用 map</x:v>
       </x:c>
-      <x:c r="H3" s="18" t="str">
+      <x:c r="H3" s="20" t="str">
         <x:v>客户端 c</x:v>
       </x:c>
-      <x:c r="I3" s="18"/>
-      <x:c r="J3" s="18"/>
-      <x:c r="K3" s="18"/>
+      <x:c r="I3" s="20"/>
+      <x:c r="J3" s="20"/>
+      <x:c r="K3" s="20"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="37"/>
-      <x:c r="B4" s="28" t="str">
+      <x:c r="A4" s="39"/>
+      <x:c r="B4" s="30" t="str">
         <x:v>TbResource</x:v>
       </x:c>
-      <x:c r="C4" s="28" t="str">
+      <x:c r="C4" s="30" t="str">
         <x:v>ResourceConfig</x:v>
       </x:c>
-      <x:c r="D4" s="29" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="28" t="str">
-        <x:v>Tables/TbResource.xlsx</x:v>
-      </x:c>
-      <x:c r="F4" s="28" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G4" s="28" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H4" s="28" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I4" s="28" t="str">
+      <x:c r="D4" s="31" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="30" t="str">
+        <x:v>Tables/z_资源_ResourceConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F4" s="30" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G4" s="30" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H4" s="30" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I4" s="30" t="str">
         <x:v>TbResource generated from Excel</x:v>
       </x:c>
-      <x:c r="J4" s="28"/>
-      <x:c r="K4" s="30"/>
+      <x:c r="J4" s="30"/>
+      <x:c r="K4" s="32"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="38"/>
-      <x:c r="B5" s="38" t="str">
+      <x:c r="A5" s="40"/>
+      <x:c r="B5" s="40" t="str">
         <x:v>TbAttribute</x:v>
       </x:c>
-      <x:c r="C5" s="38" t="str">
+      <x:c r="C5" s="40" t="str">
         <x:v>AttributeConfig</x:v>
       </x:c>
-      <x:c r="D5" s="39" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="38" t="str">
-        <x:v>Tables/TbAttribute.xlsx</x:v>
-      </x:c>
-      <x:c r="F5" s="38" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G5" s="38" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H5" s="38" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I5" s="38" t="str">
+      <x:c r="D5" s="41" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="40" t="str">
+        <x:v>Tables/s_属性_AttributeConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F5" s="40" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G5" s="40" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H5" s="40" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I5" s="40" t="str">
         <x:v>TbAttribute generated from Excel</x:v>
       </x:c>
-      <x:c r="J5" s="38"/>
-      <x:c r="K5" s="38"/>
+      <x:c r="J5" s="40"/>
+      <x:c r="K5" s="40"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="40"/>
-      <x:c r="B6" s="40" t="str">
+      <x:c r="A6" s="42"/>
+      <x:c r="B6" s="42" t="str">
         <x:v>TbItem</x:v>
       </x:c>
-      <x:c r="C6" s="40" t="str">
+      <x:c r="C6" s="42" t="str">
         <x:v>ItemConfig</x:v>
       </x:c>
-      <x:c r="D6" s="41" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="40" t="str">
-        <x:v>Tables/TbItem.xlsx</x:v>
-      </x:c>
-      <x:c r="F6" s="40" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G6" s="40" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H6" s="40" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I6" s="40" t="str">
+      <x:c r="D6" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="42" t="str">
+        <x:v>Tables/w_物品_ItemConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F6" s="42" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G6" s="42" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H6" s="42" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I6" s="42" t="str">
         <x:v>TbItem generated from Excel</x:v>
       </x:c>
-      <x:c r="J6" s="40"/>
-      <x:c r="K6" s="40"/>
+      <x:c r="J6" s="42"/>
+      <x:c r="K6" s="42"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="40"/>
-      <x:c r="B7" s="40" t="str">
+      <x:c r="A7" s="42"/>
+      <x:c r="B7" s="42" t="str">
         <x:v>TbAnimationClip</x:v>
       </x:c>
-      <x:c r="C7" s="40" t="str">
+      <x:c r="C7" s="42" t="str">
         <x:v>AnimationClipConfig</x:v>
       </x:c>
-      <x:c r="D7" s="41" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E7" s="40" t="str">
-        <x:v>Tables/TbAnimationClip.xlsx</x:v>
-      </x:c>
-      <x:c r="F7" s="40" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G7" s="40" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H7" s="40" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I7" s="40" t="str">
+      <x:c r="D7" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="42" t="str">
+        <x:v>Tables/d_动画片段_AnimationClipConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F7" s="42" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G7" s="42" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H7" s="42" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I7" s="42" t="str">
         <x:v>TbAnimationClip generated from Excel</x:v>
       </x:c>
-      <x:c r="J7" s="40"/>
-      <x:c r="K7" s="40"/>
+      <x:c r="J7" s="42"/>
+      <x:c r="K7" s="42"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="40"/>
-      <x:c r="B8" s="40" t="str">
+      <x:c r="A8" s="42"/>
+      <x:c r="B8" s="42" t="str">
         <x:v>TbVisualSet</x:v>
       </x:c>
-      <x:c r="C8" s="40" t="str">
+      <x:c r="C8" s="42" t="str">
         <x:v>VisualSetConfig</x:v>
       </x:c>
-      <x:c r="D8" s="41" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" s="40" t="str">
-        <x:v>Tables/TbVisualSet.xlsx</x:v>
-      </x:c>
-      <x:c r="F8" s="40" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G8" s="40" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H8" s="40" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I8" s="40" t="str">
+      <x:c r="D8" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="42" t="str">
+        <x:v>Tables/b_表现集合_VisualSetConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F8" s="42" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G8" s="42" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H8" s="42" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I8" s="42" t="str">
         <x:v>TbVisualSet generated from Excel</x:v>
       </x:c>
-      <x:c r="J8" s="40"/>
-      <x:c r="K8" s="40"/>
+      <x:c r="J8" s="42"/>
+      <x:c r="K8" s="42"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="40"/>
-      <x:c r="B9" s="40" t="str">
+      <x:c r="A9" s="42"/>
+      <x:c r="B9" s="42" t="str">
         <x:v>TbMap</x:v>
       </x:c>
-      <x:c r="C9" s="40" t="str">
+      <x:c r="C9" s="42" t="str">
         <x:v>MapConfig</x:v>
       </x:c>
-      <x:c r="D9" s="41" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E9" s="40" t="str">
-        <x:v>Tables/TbMap.xlsx</x:v>
-      </x:c>
-      <x:c r="F9" s="40" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G9" s="40" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H9" s="40" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I9" s="40" t="str">
+      <x:c r="D9" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="42" t="str">
+        <x:v>Tables/d_地图_MapConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F9" s="42" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G9" s="42" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H9" s="42" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I9" s="42" t="str">
         <x:v>TbMap generated from Excel</x:v>
       </x:c>
-      <x:c r="J9" s="40"/>
-      <x:c r="K9" s="40"/>
+      <x:c r="J9" s="42"/>
+      <x:c r="K9" s="42"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="40"/>
-      <x:c r="B10" s="40" t="str">
+      <x:c r="A10" s="42"/>
+      <x:c r="B10" s="42" t="str">
         <x:v>TbCharacter</x:v>
       </x:c>
-      <x:c r="C10" s="40" t="str">
+      <x:c r="C10" s="42" t="str">
         <x:v>CharacterConfig</x:v>
       </x:c>
-      <x:c r="D10" s="41" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="40" t="str">
-        <x:v>Tables/TbCharacter.xlsx</x:v>
-      </x:c>
-      <x:c r="F10" s="40" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G10" s="40" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H10" s="40" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I10" s="40" t="str">
+      <x:c r="D10" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="42" t="str">
+        <x:v>Tables/j_角色_CharacterConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F10" s="42" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G10" s="42" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H10" s="42" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I10" s="42" t="str">
         <x:v>TbCharacter generated from Excel</x:v>
       </x:c>
-      <x:c r="J10" s="40"/>
-      <x:c r="K10" s="40"/>
+      <x:c r="J10" s="42"/>
+      <x:c r="K10" s="42"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="40"/>
-      <x:c r="B11" s="40" t="str">
+      <x:c r="A11" s="42"/>
+      <x:c r="B11" s="42" t="str">
         <x:v>TbMonster</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="str">
+      <x:c r="C11" s="42" t="str">
         <x:v>MonsterConfig</x:v>
       </x:c>
-      <x:c r="D11" s="41" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E11" s="40" t="str">
-        <x:v>Tables/TbMonster.xlsx</x:v>
-      </x:c>
-      <x:c r="F11" s="40" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G11" s="40" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H11" s="40" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I11" s="40" t="str">
+      <x:c r="D11" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="42" t="str">
+        <x:v>Tables/g_怪物_MonsterConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F11" s="42" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G11" s="42" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H11" s="42" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I11" s="42" t="str">
         <x:v>TbMonster generated from Excel</x:v>
       </x:c>
-      <x:c r="J11" s="40"/>
-      <x:c r="K11" s="40"/>
+      <x:c r="J11" s="42"/>
+      <x:c r="K11" s="42"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="40"/>
-      <x:c r="B12" s="40" t="str">
+      <x:c r="A12" s="42"/>
+      <x:c r="B12" s="42" t="str">
         <x:v>TbSkill</x:v>
       </x:c>
-      <x:c r="C12" s="40" t="str">
+      <x:c r="C12" s="42" t="str">
         <x:v>SkillConfig</x:v>
       </x:c>
-      <x:c r="D12" s="41" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" s="40" t="str">
-        <x:v>Tables/TbSkill.xlsx</x:v>
-      </x:c>
-      <x:c r="F12" s="40" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G12" s="40" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H12" s="40" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I12" s="40" t="str">
+      <x:c r="D12" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="42" t="str">
+        <x:v>Tables/j_技能_SkillConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F12" s="42" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G12" s="42" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H12" s="42" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I12" s="42" t="str">
         <x:v>TbSkill generated from Excel</x:v>
       </x:c>
-      <x:c r="J12" s="40"/>
-      <x:c r="K12" s="40"/>
+      <x:c r="J12" s="42"/>
+      <x:c r="K12" s="42"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="40"/>
-      <x:c r="B13" s="40" t="str">
+      <x:c r="A13" s="42"/>
+      <x:c r="B13" s="42" t="str">
         <x:v>TbStage</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="str">
+      <x:c r="C13" s="42" t="str">
         <x:v>StageConfig</x:v>
       </x:c>
-      <x:c r="D13" s="41" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E13" s="40" t="str">
-        <x:v>Tables/TbStage.xlsx</x:v>
-      </x:c>
-      <x:c r="F13" s="40" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G13" s="40" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H13" s="40" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I13" s="40" t="str">
+      <x:c r="D13" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="42" t="str">
+        <x:v>Tables/g_关卡_StageConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F13" s="42" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G13" s="42" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H13" s="42" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I13" s="42" t="str">
         <x:v>TbStage generated from Excel</x:v>
       </x:c>
-      <x:c r="J13" s="40"/>
-      <x:c r="K13" s="40"/>
+      <x:c r="J13" s="42"/>
+      <x:c r="K13" s="42"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="42"/>
       <x:c r="B14" s="42" t="str">
-        <x:v>TbPerformanceScenario</x:v>
+        <x:v>GameConfig</x:v>
       </x:c>
       <x:c r="C14" s="42" t="str">
-        <x:v>PerformanceScenarioConfig</x:v>
+        <x:v>GameConfigData</x:v>
       </x:c>
       <x:c r="D14" s="43" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E14" s="42" t="str">
-        <x:v>Tables/TbPerformanceScenario.xlsx</x:v>
+        <x:v>Tables/y_游戏配置_GameConfig.xlsx</x:v>
       </x:c>
       <x:c r="F14" s="42" t="str">
         <x:v>id</x:v>
@@ -991,10 +1002,39 @@
         <x:v>c</x:v>
       </x:c>
       <x:c r="I14" s="42" t="str">
-        <x:v>TbPerformanceScenario generated from Excel</x:v>
+        <x:v>GameConfig generated from Excel</x:v>
       </x:c>
       <x:c r="J14" s="42"/>
       <x:c r="K14" s="42"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="44"/>
+      <x:c r="B15" s="44" t="str">
+        <x:v>TbPerformanceScenario</x:v>
+      </x:c>
+      <x:c r="C15" s="44" t="str">
+        <x:v>PerformanceScenarioConfig</x:v>
+      </x:c>
+      <x:c r="D15" s="45" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" s="44" t="str">
+        <x:v>Tables/x_性能测试_PerformanceScenarioConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F15" s="44" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G15" s="44" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H15" s="44" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I15" s="44" t="str">
+        <x:v>TbPerformanceScenario generated from Excel</x:v>
+      </x:c>
+      <x:c r="J15" s="44"/>
+      <x:c r="K15" s="44"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="1" r:id="R0cbd4bd8a5cb47c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="1" r:id="R8580ecdce07a4d49"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -58,6 +58,10 @@
       <x:sz val="9"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
   <x:fills count="7">
@@ -177,7 +181,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="64">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -359,6 +363,102 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
@@ -1036,6 +1136,209 @@
       <x:c r="J15" s="44"/>
       <x:c r="K15" s="44"/>
     </x:row>
+    <x:row r="16" ht="45" customHeight="1">
+      <x:c r="A16" s="48"/>
+      <x:c r="B16" s="48" t="str">
+        <x:v>TbAttributeProfile</x:v>
+      </x:c>
+      <x:c r="C16" s="48" t="str">
+        <x:v>AttributeProfileConfig</x:v>
+      </x:c>
+      <x:c r="D16" s="49" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" s="50" t="str">
+        <x:v>Tables/s_属性方案_AttributeProfileConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F16" s="48" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G16" s="48" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H16" s="48" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I16" s="48" t="str">
+        <x:v>TbAttributeProfile generated from Excel</x:v>
+      </x:c>
+      <x:c r="J16" s="48"/>
+      <x:c r="K16" s="48"/>
+    </x:row>
+    <x:row r="17" ht="45" customHeight="1">
+      <x:c r="A17" s="48"/>
+      <x:c r="B17" s="48" t="str">
+        <x:v>TbSkillCombat</x:v>
+      </x:c>
+      <x:c r="C17" s="48" t="str">
+        <x:v>SkillCombatConfig</x:v>
+      </x:c>
+      <x:c r="D17" s="49" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" s="50" t="str">
+        <x:v>Tables/j_技能战斗_SkillCombatConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F17" s="48" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G17" s="48" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H17" s="48" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I17" s="48" t="str">
+        <x:v>TbSkillCombat generated from Excel</x:v>
+      </x:c>
+      <x:c r="J17" s="48"/>
+      <x:c r="K17" s="48"/>
+    </x:row>
+    <x:row r="18" ht="45" customHeight="1">
+      <x:c r="A18" s="48"/>
+      <x:c r="B18" s="48" t="str">
+        <x:v>TbCombatRules</x:v>
+      </x:c>
+      <x:c r="C18" s="48" t="str">
+        <x:v>CombatRulesConfig</x:v>
+      </x:c>
+      <x:c r="D18" s="49" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E18" s="50" t="str">
+        <x:v>Tables/z_战斗规则_CombatRulesConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F18" s="48" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G18" s="48" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H18" s="48" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I18" s="48" t="str">
+        <x:v>TbCombatRules generated from Excel</x:v>
+      </x:c>
+      <x:c r="J18" s="48"/>
+      <x:c r="K18" s="48"/>
+    </x:row>
+    <x:row r="19" ht="72" customHeight="1">
+      <x:c r="A19" s="50"/>
+      <x:c r="B19" s="50" t="str">
+        <x:v>TbAnimationDirection</x:v>
+      </x:c>
+      <x:c r="C19" s="50" t="str">
+        <x:v>AnimationDirectionConfig</x:v>
+      </x:c>
+      <x:c r="D19" s="55" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" s="50" t="str">
+        <x:v>Tables/d_动画方向_AnimationDirectionConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F19" s="50" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G19" s="50" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H19" s="50" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I19" s="50" t="str">
+        <x:v>TbAnimationDirection generated from Excel</x:v>
+      </x:c>
+      <x:c r="J19" s="50"/>
+      <x:c r="K19" s="50"/>
+    </x:row>
+    <x:row r="20" ht="72" customHeight="1">
+      <x:c r="A20" s="50"/>
+      <x:c r="B20" s="50" t="str">
+        <x:v>TbCombatPresentation</x:v>
+      </x:c>
+      <x:c r="C20" s="50" t="str">
+        <x:v>CombatPresentationConfig</x:v>
+      </x:c>
+      <x:c r="D20" s="55" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E20" s="50" t="str">
+        <x:v>Tables/z_战斗表现_CombatPresentationConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F20" s="50" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G20" s="50" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H20" s="50" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I20" s="50" t="str">
+        <x:v>TbCombatPresentation generated from Excel</x:v>
+      </x:c>
+      <x:c r="J20" s="50"/>
+      <x:c r="K20" s="50"/>
+    </x:row>
+    <x:row r="21" ht="72" customHeight="1">
+      <x:c r="A21"/>
+      <x:c r="B21" s="62" t="str">
+        <x:v>TbAttackDirection</x:v>
+      </x:c>
+      <x:c r="C21" s="62" t="str">
+        <x:v>AttackDirectionConfig</x:v>
+      </x:c>
+      <x:c r="D21" s="63" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" s="62" t="str">
+        <x:v>Tables/d_攻击方向_AttackDirectionConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F21" s="62" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G21" s="62" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H21" s="62" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I21" s="62" t="str">
+        <x:v>TbAttackDirection generated from Excel</x:v>
+      </x:c>
+      <x:c r="J21" s="62"/>
+      <x:c r="K21" s="62"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22" t="str">
+        <x:v>TbHeroWeapon</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>HeroWeaponConfig</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>Tables/h_神将武器_HeroWeaponConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>神将五档武器与本体映射</x:v>
+      </x:c>
+      <x:c r="J22"/>
+      <x:c r="K22"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="1" r:id="R8580ecdce07a4d49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="1" r:id="R3960692ad2f94b89"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="9">
+  <x:fonts count="19">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -63,8 +63,68 @@
       <x:sz val="11"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF243B53"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF52606D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF52606D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF334E68"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF334E68"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -96,8 +156,28 @@
         <x:fgColor rgb="FF64748B"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F8FB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="11">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -177,11 +257,25 @@
         <x:color rgb="FFE5E7EB"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="64">
+  <x:cellXfs count="120">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -458,6 +552,246 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -684,660 +1018,892 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="34" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="27" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="8" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="8" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="8" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="33" t="str">
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="85" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B1" s="14" t="str">
+      <x:c r="B1" s="85" t="str">
         <x:v>full_name</x:v>
       </x:c>
-      <x:c r="C1" s="14" t="str">
+      <x:c r="C1" s="85" t="str">
         <x:v>value_type</x:v>
       </x:c>
-      <x:c r="D1" s="14" t="str">
+      <x:c r="D1" s="85" t="str">
         <x:v>read_schema_from_file</x:v>
       </x:c>
-      <x:c r="E1" s="14" t="str">
+      <x:c r="E1" s="85" t="str">
         <x:v>input</x:v>
       </x:c>
-      <x:c r="F1" s="14" t="str">
+      <x:c r="F1" s="85" t="str">
         <x:v>index</x:v>
       </x:c>
-      <x:c r="G1" s="14" t="str">
+      <x:c r="G1" s="85" t="str">
         <x:v>mode</x:v>
       </x:c>
-      <x:c r="H1" s="14" t="str">
+      <x:c r="H1" s="85" t="str">
         <x:v>group</x:v>
       </x:c>
-      <x:c r="I1" s="14" t="str">
+      <x:c r="I1" s="85" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="J1" s="14" t="str">
+      <x:c r="J1" s="85" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="K1" s="15" t="str">
+      <x:c r="K1" s="85" t="str">
         <x:v>output</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="37" t="str">
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="87" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B2" s="18" t="str">
+      <x:c r="B2" s="87" t="str">
         <x:v>完整表名</x:v>
       </x:c>
-      <x:c r="C2" s="18" t="str">
+      <x:c r="C2" s="87" t="str">
         <x:v>记录类型</x:v>
       </x:c>
-      <x:c r="D2" s="18" t="str">
+      <x:c r="D2" s="87" t="str">
         <x:v>从业务表读取定义</x:v>
       </x:c>
-      <x:c r="E2" s="18" t="str">
+      <x:c r="E2" s="87" t="str">
         <x:v>输入文件</x:v>
       </x:c>
-      <x:c r="F2" s="18" t="str">
+      <x:c r="F2" s="87" t="str">
         <x:v>索引字段</x:v>
       </x:c>
-      <x:c r="G2" s="18" t="str">
+      <x:c r="G2" s="87" t="str">
         <x:v>模式</x:v>
       </x:c>
-      <x:c r="H2" s="18" t="str">
+      <x:c r="H2" s="87" t="str">
         <x:v>分组</x:v>
       </x:c>
-      <x:c r="I2" s="18" t="str">
+      <x:c r="I2" s="87" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="J2" s="18"/>
-      <x:c r="K2" s="18" t="str">
+      <x:c r="J2" s="87"/>
+      <x:c r="K2" s="87" t="str">
         <x:v>输出文件</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="38" t="str">
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="90" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3" s="20"/>
-      <x:c r="C3" s="20"/>
-      <x:c r="D3" s="20" t="str">
+      <x:c r="B3" s="91"/>
+      <x:c r="C3" s="91"/>
+      <x:c r="D3" s="91" t="str">
         <x:v>必须为 true</x:v>
       </x:c>
-      <x:c r="E3" s="20"/>
-      <x:c r="F3" s="20" t="str">
+      <x:c r="E3" s="91"/>
+      <x:c r="F3" s="91" t="str">
         <x:v>统一使用 id</x:v>
       </x:c>
-      <x:c r="G3" s="20" t="str">
+      <x:c r="G3" s="91" t="str">
         <x:v>统一使用 map</x:v>
       </x:c>
-      <x:c r="H3" s="20" t="str">
+      <x:c r="H3" s="91" t="str">
         <x:v>客户端 c</x:v>
       </x:c>
-      <x:c r="I3" s="20"/>
-      <x:c r="J3" s="20"/>
-      <x:c r="K3" s="20"/>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="39"/>
-      <x:c r="B4" s="30" t="str">
+      <x:c r="I3" s="91"/>
+      <x:c r="J3" s="91"/>
+      <x:c r="K3" s="91"/>
+    </x:row>
+    <x:row r="4" ht="54" customHeight="1">
+      <x:c r="A4" s="95"/>
+      <x:c r="B4" s="96" t="str">
         <x:v>TbResource</x:v>
       </x:c>
-      <x:c r="C4" s="30" t="str">
+      <x:c r="C4" s="96" t="str">
         <x:v>ResourceConfig</x:v>
       </x:c>
-      <x:c r="D4" s="31" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="30" t="str">
+      <x:c r="D4" s="97" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="96" t="str">
         <x:v>Tables/z_资源_ResourceConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F4" s="30" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G4" s="30" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H4" s="30" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I4" s="30" t="str">
+      <x:c r="F4" s="96" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G4" s="96" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H4" s="96" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I4" s="96" t="str">
         <x:v>TbResource generated from Excel</x:v>
       </x:c>
-      <x:c r="J4" s="30"/>
-      <x:c r="K4" s="32"/>
+      <x:c r="J4" s="96"/>
+      <x:c r="K4" s="96"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="40"/>
-      <x:c r="B5" s="40" t="str">
+      <x:c r="A5" s="118"/>
+      <x:c r="B5" s="118" t="str">
         <x:v>TbAttribute</x:v>
       </x:c>
-      <x:c r="C5" s="40" t="str">
+      <x:c r="C5" s="118" t="str">
         <x:v>AttributeConfig</x:v>
       </x:c>
-      <x:c r="D5" s="41" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="40" t="str">
+      <x:c r="D5" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="118" t="str">
         <x:v>Tables/s_属性_AttributeConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F5" s="40" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G5" s="40" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H5" s="40" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I5" s="40" t="str">
+      <x:c r="F5" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G5" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H5" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I5" s="118" t="str">
         <x:v>TbAttribute generated from Excel</x:v>
       </x:c>
-      <x:c r="J5" s="40"/>
-      <x:c r="K5" s="40"/>
+      <x:c r="J5" s="118"/>
+      <x:c r="K5" s="118"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="42"/>
-      <x:c r="B6" s="42" t="str">
+      <x:c r="A6" s="118"/>
+      <x:c r="B6" s="118" t="str">
         <x:v>TbItem</x:v>
       </x:c>
-      <x:c r="C6" s="42" t="str">
+      <x:c r="C6" s="118" t="str">
         <x:v>ItemConfig</x:v>
       </x:c>
-      <x:c r="D6" s="43" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="42" t="str">
+      <x:c r="D6" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="118" t="str">
         <x:v>Tables/w_物品_ItemConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F6" s="42" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G6" s="42" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H6" s="42" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I6" s="42" t="str">
+      <x:c r="F6" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G6" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H6" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I6" s="118" t="str">
         <x:v>TbItem generated from Excel</x:v>
       </x:c>
-      <x:c r="J6" s="42"/>
-      <x:c r="K6" s="42"/>
+      <x:c r="J6" s="118"/>
+      <x:c r="K6" s="118"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="42"/>
-      <x:c r="B7" s="42" t="str">
+      <x:c r="A7" s="118"/>
+      <x:c r="B7" s="118" t="str">
         <x:v>TbAnimationClip</x:v>
       </x:c>
-      <x:c r="C7" s="42" t="str">
+      <x:c r="C7" s="118" t="str">
         <x:v>AnimationClipConfig</x:v>
       </x:c>
-      <x:c r="D7" s="43" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E7" s="42" t="str">
+      <x:c r="D7" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="118" t="str">
         <x:v>Tables/d_动画片段_AnimationClipConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F7" s="42" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G7" s="42" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H7" s="42" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I7" s="42" t="str">
+      <x:c r="F7" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G7" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H7" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I7" s="118" t="str">
         <x:v>TbAnimationClip generated from Excel</x:v>
       </x:c>
-      <x:c r="J7" s="42"/>
-      <x:c r="K7" s="42"/>
+      <x:c r="J7" s="118"/>
+      <x:c r="K7" s="118"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="42"/>
-      <x:c r="B8" s="42" t="str">
+      <x:c r="A8" s="118"/>
+      <x:c r="B8" s="118" t="str">
         <x:v>TbVisualSet</x:v>
       </x:c>
-      <x:c r="C8" s="42" t="str">
+      <x:c r="C8" s="118" t="str">
         <x:v>VisualSetConfig</x:v>
       </x:c>
-      <x:c r="D8" s="43" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" s="42" t="str">
+      <x:c r="D8" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="118" t="str">
         <x:v>Tables/b_表现集合_VisualSetConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F8" s="42" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G8" s="42" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H8" s="42" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I8" s="42" t="str">
+      <x:c r="F8" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G8" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H8" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I8" s="118" t="str">
         <x:v>TbVisualSet generated from Excel</x:v>
       </x:c>
-      <x:c r="J8" s="42"/>
-      <x:c r="K8" s="42"/>
+      <x:c r="J8" s="118"/>
+      <x:c r="K8" s="118"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="42"/>
-      <x:c r="B9" s="42" t="str">
+      <x:c r="A9" s="118"/>
+      <x:c r="B9" s="118" t="str">
         <x:v>TbMap</x:v>
       </x:c>
-      <x:c r="C9" s="42" t="str">
+      <x:c r="C9" s="118" t="str">
         <x:v>MapConfig</x:v>
       </x:c>
-      <x:c r="D9" s="43" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E9" s="42" t="str">
+      <x:c r="D9" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="118" t="str">
         <x:v>Tables/d_地图_MapConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F9" s="42" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G9" s="42" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H9" s="42" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I9" s="42" t="str">
+      <x:c r="F9" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G9" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H9" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I9" s="118" t="str">
         <x:v>TbMap generated from Excel</x:v>
       </x:c>
-      <x:c r="J9" s="42"/>
-      <x:c r="K9" s="42"/>
+      <x:c r="J9" s="118"/>
+      <x:c r="K9" s="118"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="42"/>
-      <x:c r="B10" s="42" t="str">
+      <x:c r="A10" s="118"/>
+      <x:c r="B10" s="118" t="str">
         <x:v>TbCharacter</x:v>
       </x:c>
-      <x:c r="C10" s="42" t="str">
+      <x:c r="C10" s="118" t="str">
         <x:v>CharacterConfig</x:v>
       </x:c>
-      <x:c r="D10" s="43" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="42" t="str">
+      <x:c r="D10" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="118" t="str">
         <x:v>Tables/j_角色_CharacterConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F10" s="42" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G10" s="42" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H10" s="42" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I10" s="42" t="str">
+      <x:c r="F10" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G10" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H10" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I10" s="118" t="str">
         <x:v>TbCharacter generated from Excel</x:v>
       </x:c>
-      <x:c r="J10" s="42"/>
-      <x:c r="K10" s="42"/>
+      <x:c r="J10" s="118"/>
+      <x:c r="K10" s="118"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="42"/>
-      <x:c r="B11" s="42" t="str">
+      <x:c r="A11" s="118"/>
+      <x:c r="B11" s="118" t="str">
         <x:v>TbMonster</x:v>
       </x:c>
-      <x:c r="C11" s="42" t="str">
+      <x:c r="C11" s="118" t="str">
         <x:v>MonsterConfig</x:v>
       </x:c>
-      <x:c r="D11" s="43" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E11" s="42" t="str">
+      <x:c r="D11" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="118" t="str">
         <x:v>Tables/g_怪物_MonsterConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F11" s="42" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G11" s="42" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H11" s="42" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I11" s="42" t="str">
+      <x:c r="F11" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G11" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H11" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I11" s="118" t="str">
         <x:v>TbMonster generated from Excel</x:v>
       </x:c>
-      <x:c r="J11" s="42"/>
-      <x:c r="K11" s="42"/>
+      <x:c r="J11" s="118"/>
+      <x:c r="K11" s="118"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="42"/>
-      <x:c r="B12" s="42" t="str">
+      <x:c r="A12" s="118"/>
+      <x:c r="B12" s="118" t="str">
         <x:v>TbSkill</x:v>
       </x:c>
-      <x:c r="C12" s="42" t="str">
+      <x:c r="C12" s="118" t="str">
         <x:v>SkillConfig</x:v>
       </x:c>
-      <x:c r="D12" s="43" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" s="42" t="str">
+      <x:c r="D12" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="118" t="str">
         <x:v>Tables/j_技能_SkillConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F12" s="42" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G12" s="42" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H12" s="42" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I12" s="42" t="str">
+      <x:c r="F12" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G12" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H12" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I12" s="118" t="str">
         <x:v>TbSkill generated from Excel</x:v>
       </x:c>
-      <x:c r="J12" s="42"/>
-      <x:c r="K12" s="42"/>
+      <x:c r="J12" s="118"/>
+      <x:c r="K12" s="118"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="42"/>
-      <x:c r="B13" s="42" t="str">
+      <x:c r="A13" s="118"/>
+      <x:c r="B13" s="118" t="str">
         <x:v>TbStage</x:v>
       </x:c>
-      <x:c r="C13" s="42" t="str">
+      <x:c r="C13" s="118" t="str">
         <x:v>StageConfig</x:v>
       </x:c>
-      <x:c r="D13" s="43" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E13" s="42" t="str">
+      <x:c r="D13" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="118" t="str">
         <x:v>Tables/g_关卡_StageConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F13" s="42" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G13" s="42" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H13" s="42" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I13" s="42" t="str">
+      <x:c r="F13" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G13" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H13" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I13" s="118" t="str">
         <x:v>TbStage generated from Excel</x:v>
       </x:c>
-      <x:c r="J13" s="42"/>
-      <x:c r="K13" s="42"/>
+      <x:c r="J13" s="118"/>
+      <x:c r="K13" s="118"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="42"/>
-      <x:c r="B14" s="42" t="str">
+      <x:c r="A14" s="118"/>
+      <x:c r="B14" s="118" t="str">
         <x:v>GameConfig</x:v>
       </x:c>
-      <x:c r="C14" s="42" t="str">
+      <x:c r="C14" s="118" t="str">
         <x:v>GameConfigData</x:v>
       </x:c>
-      <x:c r="D14" s="43" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E14" s="42" t="str">
+      <x:c r="D14" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" s="118" t="str">
         <x:v>Tables/y_游戏配置_GameConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F14" s="42" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G14" s="42" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H14" s="42" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I14" s="42" t="str">
+      <x:c r="F14" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G14" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H14" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I14" s="118" t="str">
         <x:v>GameConfig generated from Excel</x:v>
       </x:c>
-      <x:c r="J14" s="42"/>
-      <x:c r="K14" s="42"/>
+      <x:c r="J14" s="118"/>
+      <x:c r="K14" s="118"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="44"/>
-      <x:c r="B15" s="44" t="str">
+      <x:c r="A15" s="118"/>
+      <x:c r="B15" s="118" t="str">
         <x:v>TbPerformanceScenario</x:v>
       </x:c>
-      <x:c r="C15" s="44" t="str">
+      <x:c r="C15" s="118" t="str">
         <x:v>PerformanceScenarioConfig</x:v>
       </x:c>
-      <x:c r="D15" s="45" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E15" s="44" t="str">
+      <x:c r="D15" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" s="118" t="str">
         <x:v>Tables/x_性能测试_PerformanceScenarioConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F15" s="44" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G15" s="44" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H15" s="44" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I15" s="44" t="str">
+      <x:c r="F15" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G15" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H15" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I15" s="118" t="str">
         <x:v>TbPerformanceScenario generated from Excel</x:v>
       </x:c>
-      <x:c r="J15" s="44"/>
-      <x:c r="K15" s="44"/>
+      <x:c r="J15" s="118"/>
+      <x:c r="K15" s="118"/>
     </x:row>
     <x:row r="16" ht="45" customHeight="1">
-      <x:c r="A16" s="48"/>
-      <x:c r="B16" s="48" t="str">
+      <x:c r="A16" s="118"/>
+      <x:c r="B16" s="118" t="str">
         <x:v>TbAttributeProfile</x:v>
       </x:c>
-      <x:c r="C16" s="48" t="str">
+      <x:c r="C16" s="118" t="str">
         <x:v>AttributeProfileConfig</x:v>
       </x:c>
-      <x:c r="D16" s="49" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E16" s="50" t="str">
+      <x:c r="D16" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" s="118" t="str">
         <x:v>Tables/s_属性方案_AttributeProfileConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F16" s="48" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G16" s="48" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H16" s="48" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I16" s="48" t="str">
+      <x:c r="F16" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G16" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H16" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I16" s="118" t="str">
         <x:v>TbAttributeProfile generated from Excel</x:v>
       </x:c>
-      <x:c r="J16" s="48"/>
-      <x:c r="K16" s="48"/>
+      <x:c r="J16" s="118"/>
+      <x:c r="K16" s="118"/>
     </x:row>
     <x:row r="17" ht="45" customHeight="1">
-      <x:c r="A17" s="48"/>
-      <x:c r="B17" s="48" t="str">
+      <x:c r="A17" s="118"/>
+      <x:c r="B17" s="118" t="str">
         <x:v>TbSkillCombat</x:v>
       </x:c>
-      <x:c r="C17" s="48" t="str">
+      <x:c r="C17" s="118" t="str">
         <x:v>SkillCombatConfig</x:v>
       </x:c>
-      <x:c r="D17" s="49" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E17" s="50" t="str">
+      <x:c r="D17" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" s="118" t="str">
         <x:v>Tables/j_技能战斗_SkillCombatConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F17" s="48" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G17" s="48" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H17" s="48" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I17" s="48" t="str">
+      <x:c r="F17" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G17" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H17" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I17" s="118" t="str">
         <x:v>TbSkillCombat generated from Excel</x:v>
       </x:c>
-      <x:c r="J17" s="48"/>
-      <x:c r="K17" s="48"/>
+      <x:c r="J17" s="118"/>
+      <x:c r="K17" s="118"/>
     </x:row>
     <x:row r="18" ht="45" customHeight="1">
-      <x:c r="A18" s="48"/>
-      <x:c r="B18" s="48" t="str">
+      <x:c r="A18" s="118"/>
+      <x:c r="B18" s="118" t="str">
         <x:v>TbCombatRules</x:v>
       </x:c>
-      <x:c r="C18" s="48" t="str">
+      <x:c r="C18" s="118" t="str">
         <x:v>CombatRulesConfig</x:v>
       </x:c>
-      <x:c r="D18" s="49" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E18" s="50" t="str">
+      <x:c r="D18" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E18" s="118" t="str">
         <x:v>Tables/z_战斗规则_CombatRulesConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F18" s="48" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G18" s="48" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H18" s="48" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I18" s="48" t="str">
+      <x:c r="F18" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G18" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H18" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I18" s="118" t="str">
         <x:v>TbCombatRules generated from Excel</x:v>
       </x:c>
-      <x:c r="J18" s="48"/>
-      <x:c r="K18" s="48"/>
+      <x:c r="J18" s="118"/>
+      <x:c r="K18" s="118"/>
     </x:row>
     <x:row r="19" ht="72" customHeight="1">
-      <x:c r="A19" s="50"/>
-      <x:c r="B19" s="50" t="str">
+      <x:c r="A19" s="118"/>
+      <x:c r="B19" s="118" t="str">
         <x:v>TbAnimationDirection</x:v>
       </x:c>
-      <x:c r="C19" s="50" t="str">
+      <x:c r="C19" s="118" t="str">
         <x:v>AnimationDirectionConfig</x:v>
       </x:c>
-      <x:c r="D19" s="55" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E19" s="50" t="str">
+      <x:c r="D19" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" s="118" t="str">
         <x:v>Tables/d_动画方向_AnimationDirectionConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F19" s="50" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G19" s="50" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H19" s="50" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I19" s="50" t="str">
+      <x:c r="F19" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G19" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H19" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I19" s="118" t="str">
         <x:v>TbAnimationDirection generated from Excel</x:v>
       </x:c>
-      <x:c r="J19" s="50"/>
-      <x:c r="K19" s="50"/>
+      <x:c r="J19" s="118"/>
+      <x:c r="K19" s="118"/>
     </x:row>
     <x:row r="20" ht="72" customHeight="1">
-      <x:c r="A20" s="50"/>
-      <x:c r="B20" s="50" t="str">
+      <x:c r="A20" s="118"/>
+      <x:c r="B20" s="118" t="str">
         <x:v>TbCombatPresentation</x:v>
       </x:c>
-      <x:c r="C20" s="50" t="str">
+      <x:c r="C20" s="118" t="str">
         <x:v>CombatPresentationConfig</x:v>
       </x:c>
-      <x:c r="D20" s="55" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E20" s="50" t="str">
+      <x:c r="D20" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E20" s="118" t="str">
         <x:v>Tables/z_战斗表现_CombatPresentationConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F20" s="50" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G20" s="50" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H20" s="50" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I20" s="50" t="str">
+      <x:c r="F20" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G20" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H20" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I20" s="118" t="str">
         <x:v>TbCombatPresentation generated from Excel</x:v>
       </x:c>
-      <x:c r="J20" s="50"/>
-      <x:c r="K20" s="50"/>
+      <x:c r="J20" s="118"/>
+      <x:c r="K20" s="118"/>
     </x:row>
     <x:row r="21" ht="72" customHeight="1">
-      <x:c r="A21"/>
-      <x:c r="B21" s="62" t="str">
+      <x:c r="A21" s="118"/>
+      <x:c r="B21" s="118" t="str">
         <x:v>TbAttackDirection</x:v>
       </x:c>
-      <x:c r="C21" s="62" t="str">
+      <x:c r="C21" s="118" t="str">
         <x:v>AttackDirectionConfig</x:v>
       </x:c>
-      <x:c r="D21" s="63" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E21" s="62" t="str">
+      <x:c r="D21" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" s="118" t="str">
         <x:v>Tables/d_攻击方向_AttackDirectionConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F21" s="62" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G21" s="62" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H21" s="62" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I21" s="62" t="str">
+      <x:c r="F21" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G21" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H21" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I21" s="118" t="str">
         <x:v>TbAttackDirection generated from Excel</x:v>
       </x:c>
-      <x:c r="J21" s="62"/>
-      <x:c r="K21" s="62"/>
+      <x:c r="J21" s="118"/>
+      <x:c r="K21" s="118"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22"/>
-      <x:c r="B22" t="str">
+      <x:c r="A22" s="118"/>
+      <x:c r="B22" s="118" t="str">
         <x:v>TbHeroWeapon</x:v>
       </x:c>
-      <x:c r="C22" t="str">
+      <x:c r="C22" s="118" t="str">
         <x:v>HeroWeaponConfig</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E22" t="str">
+      <x:c r="D22" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" s="118" t="str">
         <x:v>Tables/h_神将武器_HeroWeaponConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F22" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G22" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H22" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I22" t="str">
+      <x:c r="F22" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G22" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H22" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I22" s="118" t="str">
         <x:v>神将五档武器与本体映射</x:v>
       </x:c>
-      <x:c r="J22"/>
-      <x:c r="K22"/>
+      <x:c r="J22" s="118"/>
+      <x:c r="K22" s="118"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="118"/>
+      <x:c r="B23" s="118" t="str">
+        <x:v>TbStageRule</x:v>
+      </x:c>
+      <x:c r="C23" s="118" t="str">
+        <x:v>StageRuleConfig</x:v>
+      </x:c>
+      <x:c r="D23" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" s="118" t="str">
+        <x:v>Tables/g_关卡规则_StageRuleConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F23" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G23" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H23" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I23" s="118" t="str">
+        <x:v>TbStageRule generated from Excel</x:v>
+      </x:c>
+      <x:c r="J23" s="118"/>
+      <x:c r="K23" s="118"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="118"/>
+      <x:c r="B24" s="118" t="str">
+        <x:v>TbSpawnPhase</x:v>
+      </x:c>
+      <x:c r="C24" s="118" t="str">
+        <x:v>SpawnPhaseConfig</x:v>
+      </x:c>
+      <x:c r="D24" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E24" s="118" t="str">
+        <x:v>Tables/s_刷新阶段_SpawnPhaseConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F24" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G24" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H24" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I24" s="118" t="str">
+        <x:v>TbSpawnPhase generated from Excel</x:v>
+      </x:c>
+      <x:c r="J24" s="118"/>
+      <x:c r="K24" s="118"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="118"/>
+      <x:c r="B25" s="118" t="str">
+        <x:v>TbBossEncounter</x:v>
+      </x:c>
+      <x:c r="C25" s="118" t="str">
+        <x:v>BossEncounterConfig</x:v>
+      </x:c>
+      <x:c r="D25" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E25" s="118" t="str">
+        <x:v>Tables/b_Boss遭遇_BossEncounterConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F25" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G25" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H25" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I25" s="118" t="str">
+        <x:v>TbBossEncounter generated from Excel</x:v>
+      </x:c>
+      <x:c r="J25" s="118"/>
+      <x:c r="K25" s="118"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="118"/>
+      <x:c r="B26" s="118" t="str">
+        <x:v>TbExperienceLevel</x:v>
+      </x:c>
+      <x:c r="C26" s="118" t="str">
+        <x:v>ExperienceLevelConfig</x:v>
+      </x:c>
+      <x:c r="D26" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" s="118" t="str">
+        <x:v>Tables/j_经验等级_ExperienceLevelConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F26" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G26" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H26" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I26" s="118" t="str">
+        <x:v>TbExperienceLevel generated from Excel</x:v>
+      </x:c>
+      <x:c r="J26" s="118"/>
+      <x:c r="K26" s="118"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="118"/>
+      <x:c r="B27" s="118" t="str">
+        <x:v>TbDropProfile</x:v>
+      </x:c>
+      <x:c r="C27" s="118" t="str">
+        <x:v>DropProfileConfig</x:v>
+      </x:c>
+      <x:c r="D27" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="118" t="str">
+        <x:v>Tables/d_掉落_DropProfileConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F27" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G27" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H27" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I27" s="118" t="str">
+        <x:v>TbDropProfile generated from Excel</x:v>
+      </x:c>
+      <x:c r="J27" s="118"/>
+      <x:c r="K27" s="118"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="118"/>
+      <x:c r="B28" s="118" t="str">
+        <x:v>TbUpgradePool</x:v>
+      </x:c>
+      <x:c r="C28" s="118" t="str">
+        <x:v>UpgradePoolConfig</x:v>
+      </x:c>
+      <x:c r="D28" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E28" s="118" t="str">
+        <x:v>Tables/s_升级池_UpgradePoolConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F28" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G28" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H28" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I28" s="118" t="str">
+        <x:v>TbUpgradePool generated from Excel</x:v>
+      </x:c>
+      <x:c r="J28" s="118"/>
+      <x:c r="K28" s="118"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="118"/>
+      <x:c r="B29" s="118" t="str">
+        <x:v>TbUpgradeOption</x:v>
+      </x:c>
+      <x:c r="C29" s="118" t="str">
+        <x:v>UpgradeOptionConfig</x:v>
+      </x:c>
+      <x:c r="D29" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E29" s="118" t="str">
+        <x:v>Tables/s_升级选项_UpgradeOptionConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F29" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G29" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H29" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I29" s="118" t="str">
+        <x:v>TbUpgradeOption generated from Excel</x:v>
+      </x:c>
+      <x:c r="J29" s="118"/>
+      <x:c r="K29" s="118"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="118"/>
+      <x:c r="B30" s="118" t="str">
+        <x:v>TbCombatUiSet</x:v>
+      </x:c>
+      <x:c r="C30" s="118" t="str">
+        <x:v>CombatUiSetConfig</x:v>
+      </x:c>
+      <x:c r="D30" s="119" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E30" s="118" t="str">
+        <x:v>Tables/z_战斗界面_CombatUiSetConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F30" s="118" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G30" s="118" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H30" s="118" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I30" s="118" t="str">
+        <x:v>TbCombatUiSet generated from Excel</x:v>
+      </x:c>
+      <x:c r="J30" s="118"/>
+      <x:c r="K30" s="118"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
